--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/SparklinesColumnGroup/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/SparklinesColumnGroup/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R52f3e314dcd04cc1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rccf2191038544ca5"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/SparklinesColumnGroup/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/SparklinesColumnGroup/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rccf2191038544ca5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rd253d522219e4c0b"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/SparklinesColumnGroup/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/SparklinesColumnGroup/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rd253d522219e4c0b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R06bae10774e14090"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/SparklinesColumnGroup/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/SparklinesColumnGroup/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R06bae10774e14090"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R5fe3849ad250432a"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/SparklinesColumnGroup/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/SparklinesColumnGroup/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R5fe3849ad250432a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R3e645fe5c1c24ba7"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/SparklinesColumnGroup/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/SparklinesColumnGroup/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R3e645fe5c1c24ba7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R834cf4064e714936"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/SparklinesColumnGroup/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/SparklinesColumnGroup/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R834cf4064e714936"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R9bc68ba5eed8461b"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/SparklinesColumnGroup/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/SparklinesColumnGroup/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R9bc68ba5eed8461b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R62616f8fd0d34620"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/SparklinesColumnGroup/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/SparklinesColumnGroup/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R62616f8fd0d34620"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R068949333b95487b"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/SparklinesColumnGroup/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/SparklinesColumnGroup/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R068949333b95487b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R21b6734202b04d16"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/SparklinesColumnGroup/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/SparklinesColumnGroup/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R21b6734202b04d16"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R21092c346c1b44d4"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/SparklinesColumnGroup/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/SparklinesColumnGroup/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R21092c346c1b44d4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Raf9212876f2a4e61"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/SparklinesColumnGroup/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/SparklinesColumnGroup/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Raf9212876f2a4e61"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rdcf41fe0d136445d"/>
   </x:sheets>
 </x:workbook>
 </file>
